--- a/Ujian/Data.xlsx
+++ b/Ujian/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\bahasa-terbaru\Ujian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D324EDC-0777-4579-99D8-9E24ECE810CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21257F4-A8F6-4FC1-A58D-B311D77252E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Ahmad Abdullah Kholis</t>
   </si>
@@ -197,24 +197,9 @@
     <t>Umar Abdurrosyid Assary</t>
   </si>
   <si>
-    <t>Zen</t>
-  </si>
-  <si>
-    <t>Zaky</t>
-  </si>
-  <si>
-    <t>Hanip</t>
-  </si>
-  <si>
-    <t>Latip</t>
-  </si>
-  <si>
     <t>Ustadz Iman</t>
   </si>
   <si>
-    <t>Marwa</t>
-  </si>
-  <si>
     <t>Ustadzah Rahmah</t>
   </si>
   <si>
@@ -234,13 +219,37 @@
   </si>
   <si>
     <t>Ustadzah Marwa</t>
+  </si>
+  <si>
+    <t>Nama Penguji</t>
+  </si>
+  <si>
+    <t>Santri 1</t>
+  </si>
+  <si>
+    <t>Santri 2</t>
+  </si>
+  <si>
+    <t>Santri 3</t>
+  </si>
+  <si>
+    <t>Santri 4</t>
+  </si>
+  <si>
+    <t>Santri 5</t>
+  </si>
+  <si>
+    <t>Santri 6</t>
+  </si>
+  <si>
+    <t>Santri 7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +270,12 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -315,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -335,28 +350,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -639,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -648,368 +657,329 @@
     <col min="7" max="8" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
         <v>62</v>
       </c>
       <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>64</v>
       </c>
       <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>57</v>
       </c>
-      <c r="F1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J8">
-        <f>32/5</f>
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E9" s="1"/>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E12" s="4"/>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ujian/Data.xlsx
+++ b/Ujian/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\bahasa-terbaru\Ujian\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\bahasa-terbaru\Ujian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21257F4-A8F6-4FC1-A58D-B311D77252E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4E6078-0CE7-43C7-A25E-C14D82687566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Ahmad Abdullah Kholis</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Ustadzah Rahmah</t>
   </si>
   <si>
-    <t>Ustadzah Maysarah</t>
-  </si>
-  <si>
     <t>Ustadz Zen</t>
   </si>
   <si>
@@ -243,6 +240,12 @@
   </si>
   <si>
     <t>Santri 7</t>
+  </si>
+  <si>
+    <t>Ustadzah Rania</t>
+  </si>
+  <si>
+    <t>Ustadz Yuda</t>
   </si>
 </sst>
 </file>
@@ -330,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -353,19 +356,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -648,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -658,34 +652,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -705,13 +699,10 @@
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -731,13 +722,10 @@
       <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>14</v>
@@ -754,13 +742,10 @@
       <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>21</v>
@@ -776,9 +761,6 @@
       </c>
       <c r="F5" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -800,183 +782,107 @@
       <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
